--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132122911</v>
       </c>
       <c r="B2" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>132122909</v>
       </c>
       <c r="B3" t="n">
-        <v>58284</v>
+        <v>58286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>132122909</v>
       </c>
       <c r="B3" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132122911</v>
       </c>
       <c r="B2" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>132122909</v>
       </c>
       <c r="B3" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132122911</v>
       </c>
       <c r="B2" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>132122909</v>
       </c>
       <c r="B3" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132122911</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>132122909</v>
       </c>
       <c r="B3" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,6 +1014,369 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133719011</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104642</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>504532</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6612459</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På flera platser i området.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133719069</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101240</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>504532</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6612459</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridd i området.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133719024</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>504532</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6612459</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spridd i området.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>133719011</v>
       </c>
       <c r="B5" t="n">
-        <v>104642</v>
+        <v>104644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>133719069</v>
       </c>
       <c r="B6" t="n">
-        <v>101240</v>
+        <v>101242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>133719024</v>
       </c>
       <c r="B7" t="n">
-        <v>99154</v>
+        <v>99156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>133719011</v>
       </c>
       <c r="B5" t="n">
-        <v>104644</v>
+        <v>104652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>133719069</v>
       </c>
       <c r="B6" t="n">
-        <v>101242</v>
+        <v>101250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>133719024</v>
       </c>
       <c r="B7" t="n">
-        <v>99156</v>
+        <v>99164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,6 +1377,129 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134081776</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504445</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6612489</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>133407843</v>
       </c>
       <c r="B4" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>133719011</v>
       </c>
       <c r="B5" t="n">
-        <v>104652</v>
+        <v>104680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>133719069</v>
       </c>
       <c r="B6" t="n">
-        <v>101250</v>
+        <v>101278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>133719024</v>
       </c>
       <c r="B7" t="n">
-        <v>99164</v>
+        <v>99192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>134081776</v>
       </c>
       <c r="B8" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>133407843</v>
       </c>
       <c r="B4" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>133719011</v>
       </c>
       <c r="B5" t="n">
-        <v>104680</v>
+        <v>104690</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>133719069</v>
       </c>
       <c r="B6" t="n">
-        <v>101278</v>
+        <v>101288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>133719024</v>
       </c>
       <c r="B7" t="n">
-        <v>99192</v>
+        <v>99202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>134081776</v>
       </c>
       <c r="B8" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>133719011</v>
       </c>
       <c r="B5" t="n">
-        <v>104690</v>
+        <v>104692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>133719069</v>
       </c>
       <c r="B6" t="n">
-        <v>101288</v>
+        <v>101290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>133719024</v>
       </c>
       <c r="B7" t="n">
-        <v>99202</v>
+        <v>99204</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>133719011</v>
       </c>
       <c r="B5" t="n">
-        <v>104693</v>
+        <v>104700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>133719069</v>
       </c>
       <c r="B6" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>133719024</v>
       </c>
       <c r="B7" t="n">
-        <v>99205</v>
+        <v>99212</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>132122911</v>
       </c>
       <c r="B2" t="n">
-        <v>57951</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -784,60 +784,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132122909</v>
+        <v>134381783</v>
       </c>
       <c r="B3" t="n">
-        <v>58328</v>
+        <v>58260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Lejaskogen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504538</v>
+        <v>504459</v>
       </c>
       <c r="R3" t="n">
-        <v>6612450</v>
+        <v>6612553</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,44 +891,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133407843</v>
+        <v>134381804</v>
       </c>
       <c r="B4" t="n">
-        <v>58349</v>
+        <v>58260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504530</v>
+        <v>504533</v>
       </c>
       <c r="R4" t="n">
-        <v>6612516</v>
+        <v>6612560</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,17 +984,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1016,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133719011</v>
+        <v>132122909</v>
       </c>
       <c r="B5" t="n">
-        <v>104700</v>
+        <v>58349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,41 +1041,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lejaskogen, Vstm</t>
+          <t>Leja, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504532</v>
+        <v>504538</v>
       </c>
       <c r="R5" t="n">
-        <v>6612459</v>
+        <v>6612450</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,27 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>03:00</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera platser i området.</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,33 +1121,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133719069</v>
+        <v>133407843</v>
       </c>
       <c r="B6" t="n">
-        <v>101298</v>
+        <v>58349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,27 +1150,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504532</v>
+        <v>504530</v>
       </c>
       <c r="R6" t="n">
-        <v>6612459</v>
+        <v>6612516</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,27 +1216,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spridd i området.</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1240,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133719024</v>
+        <v>133718953</v>
       </c>
       <c r="B7" t="n">
-        <v>99212</v>
+        <v>58349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,27 +1273,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504532</v>
+        <v>504490</v>
       </c>
       <c r="R7" t="n">
-        <v>6612459</v>
+        <v>6612437</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1345,18 +1357,12 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spridd i området.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1495,6 +1501,490 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133719024</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>504532</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6612459</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spridd i området.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133719011</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>504532</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6612459</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På flera platser i området.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133719069</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>504532</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6612459</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spridd i området.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133719030</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lejaskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>504532</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6612459</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spridd i området.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 8189-2026 artfynd.xlsx
+++ b/artfynd/A 8189-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122911</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134381783</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134381804</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122909</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1259,6 +1284,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133407843</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133718953</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1503,6 +1538,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081776</t>
         </is>
       </c>
     </row>
@@ -1626,6 +1666,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719024</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1747,6 +1792,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719011</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1868,6 +1918,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719069</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1989,8 +2044,26 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133719030</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>